--- a/docs/downloads/04/tbl_other_act_all_alaotra_ambodivoara.xlsx
+++ b/docs/downloads/04/tbl_other_act_all_alaotra_ambodivoara.xlsx
@@ -387,12 +387,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -405,12 +399,6 @@
           <t>Activités domestiques - Asa an-trano</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -423,12 +411,6 @@
           <t>Autres activités libérales - Asa mahaleo-tena hafa</t>
         </is>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -441,12 +423,6 @@
           <t>Collecteur (riz) - Mpanangom-bary</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -513,12 +489,6 @@
           <t>Employé du secteur tertiaire (commerce, administration, service) : gérant, agent, secrétaire, caissier, vendeur, comptable, aide-comptable,... - Mpiasa amin?ny fandraharahana momba ny varotra, mpitantsoratra, mpandray vola, mpitantambola na ny mpanampy az</t>
         </is>
       </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -531,12 +501,6 @@
           <t>Enseignant du secondaire - Mpampianatra @ Ambaratonga faharoa</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -549,12 +513,6 @@
           <t>Gardien de bétail (Salarié) - Mpikarama miandry omby</t>
         </is>
       </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -585,12 +543,6 @@
           <t>Membre d?un ménage mais employé permanent chez un autre ménage ? Olona mpikambana ao @ tokantrano iray fa mpiasa raikitra any @ tokantrano hafa</t>
         </is>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -621,12 +573,6 @@
           <t>Ouvrier d'entretien, bricoleur (kibaroa) - Kibaroa, manao izay asa hita</t>
         </is>
       </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -639,12 +585,6 @@
           <t>Salarié en élevage- Mpikarama @ fiompiana</t>
         </is>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -670,12 +610,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -688,12 +622,6 @@
           <t>Activités domestiques - Asa an-trano</t>
         </is>
       </c>
-      <c r="C19">
-        <v>4</v>
-      </c>
-      <c r="D19">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -706,12 +634,6 @@
           <t>Aide Sanitaire</t>
         </is>
       </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="D20">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -724,12 +646,6 @@
           <t>Artisan NCA (exerçant un métier manuel à son propre compte) - Mpanao asa tanana tsy voasokajy teo aloha miasa tena</t>
         </is>
       </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -742,12 +658,6 @@
           <t>Autres activités libérales - Asa mahaleo-tena hafa</t>
         </is>
       </c>
-      <c r="C22">
-        <v>4</v>
-      </c>
-      <c r="D22">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -760,12 +670,6 @@
           <t>Coiffeur-Mpanety, mpanao volo</t>
         </is>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -778,12 +682,6 @@
           <t>Collecteur (riz) - Mpanangom-bary</t>
         </is>
       </c>
-      <c r="C24">
-        <v>2</v>
-      </c>
-      <c r="D24">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -814,12 +712,6 @@
           <t>Conducteur de véhicule, engin, transporteur camion et voiture - Mpamily fiara, Mpitatitra @ fiara, fiarabe?</t>
         </is>
       </c>
-      <c r="C26">
-        <v>3</v>
-      </c>
-      <c r="D26">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -832,12 +724,6 @@
           <t>Couturier, tailleur - Mpanjaitra</t>
         </is>
       </c>
-      <c r="C27">
-        <v>2</v>
-      </c>
-      <c r="D27">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -850,12 +736,6 @@
           <t>Cueillette (produit naturel ou collecte sauvage) - Mpioty vokatra voajanahary, tsy nambolena</t>
         </is>
       </c>
-      <c r="C28">
-        <v>3</v>
-      </c>
-      <c r="D28">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -886,12 +766,6 @@
           <t>Docker, manutentionnaire, porteur - Mpibata entana, Mpanao kibaroa</t>
         </is>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -940,12 +814,6 @@
           <t>Employé du secteur tertiaire (commerce, administration, service) : gérant, agent, secrétaire, caissier, vendeur, comptable, aide-comptable,... - Mpiasa amin?ny fandraharahana momba ny varotra, mpitantsoratra, mpandray vola, mpitantambola na ny mpanampy az</t>
         </is>
       </c>
-      <c r="C33">
-        <v>2</v>
-      </c>
-      <c r="D33">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -976,12 +844,6 @@
           <t>Enseignant du primaire - Mpampianatra @ fanabeazana fototra</t>
         </is>
       </c>
-      <c r="C35">
-        <v>3</v>
-      </c>
-      <c r="D35">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -994,12 +856,6 @@
           <t>Enseignant du secondaire - Mpampianatra @ Ambaratonga faharoa</t>
         </is>
       </c>
-      <c r="C36">
-        <v>2</v>
-      </c>
-      <c r="D36">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1030,12 +886,6 @@
           <t>Gardien de bétail (Salarié) - Mpikarama miandry omby</t>
         </is>
       </c>
-      <c r="C38">
-        <v>3</v>
-      </c>
-      <c r="D38">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1048,12 +898,6 @@
           <t>Gardien, agent de sécurité (privé), concierge - Mpiambina, Mpiandraikitra ny fandriampahalemana, Mpandray olona</t>
         </is>
       </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1102,12 +946,6 @@
           <t>Maçon, Ouvrier du bâtiment, peintre en bâtiment, Plombier - Mpandalotra, Mpiasa @ taotrano, Mpiasa mikarakara ny rano</t>
         </is>
       </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1138,12 +976,6 @@
           <t>Mécanicien- Mpanamboatra fiarakodia</t>
         </is>
       </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1192,12 +1024,6 @@
           <t>Potier, Mouleur de brique et de tuile à la main Mpanamboatra tavim-boninkazo, biriky, taila amin?ny tanana</t>
         </is>
       </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="D47">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1210,12 +1036,6 @@
           <t>Pépiniériste,Horticulteur (plantesd'ornement), fleuriste - Mpikarakara zanakazo, Mpamboly voninkazo</t>
         </is>
       </c>
-      <c r="C48">
-        <v>2</v>
-      </c>
-      <c r="D48">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1228,12 +1048,6 @@
           <t>Pêcheur exploitant- Mpanjono miasa tena</t>
         </is>
       </c>
-      <c r="C49">
-        <v>3</v>
-      </c>
-      <c r="D49">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1246,12 +1060,6 @@
           <t>Sage-femme, infirmier - Mpampivelona, mpitsabo mpanampy</t>
         </is>
       </c>
-      <c r="C50">
-        <v>2</v>
-      </c>
-      <c r="D50">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1281,12 +1089,6 @@
         <is>
           <t>Taxi-bicyclette</t>
         </is>
-      </c>
-      <c r="C52">
-        <v>2</v>
-      </c>
-      <c r="D52">
-        <v>0.1</v>
       </c>
     </row>
     <row r="53">
